--- a/data/sjcl1.xlsx
+++ b/data/sjcl1.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="实际产量统计" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,29 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCE6F1"/>
+        <bgColor rgb="00DCE6F1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +55,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,208 +450,233 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr"/>
-      <c r="B1" t="inlineStr"/>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
-      <c r="G1" t="inlineStr"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>集团所属煤矿原煤实际产量统计表</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>集团所属煤矿原煤实际产量统计表</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>指标</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>指标</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>煤矿名称</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>月计划量(吨)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>当日原煤实际产量(吨)</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>完成率(%)</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>年累计原煤实际产量(吨)</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>煤矿名称</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>月计划量(吨)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>当日原煤实际产量(吨)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>完成率(%)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>年累计原煤实际产量(吨)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
+      <c r="A4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>郭家山煤矿</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="7">
+        <f>D4/(C4/30)*100</f>
+        <v/>
+      </c>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>郭家山煤矿</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="A5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>姚家村煤矿</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="7">
+        <f>D5/(C5/30)*100</f>
+        <v/>
+      </c>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>姚家村煤矿</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>250000</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="A6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>金所煤矿</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="7">
+        <f>D6/(C6/30)*100</f>
+        <v/>
+      </c>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>金所煤矿</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>200000</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="A7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>芒东二矿</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>180000</v>
+      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="7">
+        <f>D7/(C7/30)*100</f>
+        <v/>
+      </c>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>芒东二矿</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>180000</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="A8" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>胜利煤矿</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="7">
+        <f>D8/(C8/30)*100</f>
+        <v/>
+      </c>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>胜利煤矿</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>150000</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="A9" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>竜浪煤矿</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="7">
+        <f>D9/(C9/30)*100</f>
+        <v/>
+      </c>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>竜浪煤矿</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>120000</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="A10" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>双河煤矿</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="7">
+        <f>D10/(C10/30)*100</f>
+        <v/>
+      </c>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>双河煤矿</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="10">
+        <f>SUM(D4:D10)</f>
+        <v/>
+      </c>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="10">
+        <f>SUM(F4:F10)</f>
+        <v/>
+      </c>
+      <c r="G11" s="9" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/sjcl1.xlsx
+++ b/data/sjcl1.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\ymky_manager\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F5E366C-4933-4394-A2F7-58EB4070DE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4466829-CD1B-4619-ACC9-602DE703D67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
+    <workbookView xWindow="1080" yWindow="3720" windowWidth="13740" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -90,7 +90,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
@@ -574,7 +574,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="3" defaultTableStyle="TableStylePreset8_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset8_Accent1 1" pivot="0" count="7">
+    <tableStyle name="TableStylePreset8_Accent1 1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="25"/>
       <tableStyleElement type="headerRow" dxfId="24"/>
       <tableStyleElement type="totalRow" dxfId="23"/>
@@ -583,7 +583,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="20"/>
       <tableStyleElement type="firstColumnStripe" dxfId="19"/>
     </tableStyle>
-    <tableStyle name="TableStylePreset8_Accent1" pivot="0" count="9">
+    <tableStyle name="TableStylePreset8_Accent1" pivot="0" count="9" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="wholeTable" dxfId="18"/>
       <tableStyleElement type="headerRow" dxfId="17"/>
       <tableStyleElement type="totalRow" dxfId="16"/>
@@ -594,7 +594,7 @@
       <tableStyleElement type="firstColumnStripe" dxfId="11"/>
       <tableStyleElement type="secondColumnStripe" dxfId="10"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
       <tableStyleElement type="headerRow" dxfId="9"/>
       <tableStyleElement type="totalRow" dxfId="8"/>
       <tableStyleElement type="firstRowStripe" dxfId="7"/>
@@ -867,7 +867,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
@@ -925,7 +925,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="4">
-        <v>3666.6666666666665</v>
+        <v>3333</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="2">
@@ -940,7 +940,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="6">
-        <v>2333.3333333333335</v>
+        <v>2667</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="2">
@@ -1051,13 +1051,13 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter scaleWithDoc="0" alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <sheetData/>
@@ -1069,7 +1069,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <sheetData/>
